--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="304">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -808,6 +808,9 @@
   </si>
   <si>
     <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214809534256589</t>
@@ -999,7 +1002,7 @@
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1039,6 +1042,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFe8384f"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1084,7 +1092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1103,6 +1111,7 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5740,7 +5749,7 @@
         <v>46252.60736721064</v>
       </c>
       <c r="D72" s="5">
-        <v>46252.60738498843</v>
+        <v>46280.13412778935</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>247</v>
@@ -5784,8 +5793,8 @@
       <c r="R72" s="5">
         <v>46287</v>
       </c>
-      <c r="S72" s="7" t="s">
-        <v>33</v>
+      <c r="S72" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -5796,7 +5805,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5849,7 +5858,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5861,7 +5870,7 @@
         <v>46243.72785484954</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5914,7 +5923,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5951,13 +5960,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5967,7 +5976,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5979,7 +5988,7 @@
         <v>46243.72789628472</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6032,7 +6041,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6069,13 +6078,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6085,7 +6094,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6095,7 +6104,7 @@
         <v>46260.58012614583</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6148,7 +6157,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6185,13 +6194,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6201,7 +6210,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6211,7 +6220,7 @@
         <v>46260.58014068287</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6264,7 +6273,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6301,13 +6310,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6317,7 +6326,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6327,7 +6336,7 @@
         <v>46260.580162743056</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6360,7 +6369,7 @@
         <v>189</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6380,7 +6389,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6417,13 +6426,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>187</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6433,7 +6442,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6443,7 +6452,7 @@
         <v>46260.57978292824</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6467,7 +6476,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6480,7 +6489,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6490,16 +6499,16 @@
         <v>46243.72816118055</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6517,13 +6526,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6543,7 +6552,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6559,10 +6568,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6580,13 +6589,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6596,7 +6605,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6608,7 +6617,7 @@
         <v>46260.579793020835</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6633,13 +6642,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6659,7 +6668,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6696,13 +6705,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6712,7 +6721,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6724,7 +6733,7 @@
         <v>46260.579739768524</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6751,13 +6760,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6777,7 +6786,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6816,13 +6825,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6832,7 +6841,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6842,7 +6851,7 @@
         <v>46243.72830107639</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6869,13 +6878,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6895,7 +6904,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6930,13 +6939,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6946,7 +6955,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6956,7 +6965,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6980,7 +6989,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6993,7 +7002,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -7003,16 +7012,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7030,13 +7039,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7056,7 +7065,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7066,7 +7075,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7093,13 +7102,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5867,7 +5867,7 @@
         <v>46213.50741020833</v>
       </c>
       <c r="D74" s="5">
-        <v>46243.72785484954</v>
+        <v>46282.14852243055</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>252</v>
@@ -5911,8 +5911,8 @@
       <c r="R74" s="5">
         <v>46289</v>
       </c>
-      <c r="S74" s="7" t="s">
-        <v>33</v>
+      <c r="S74" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
